--- a/src/ii_skills/shared/excel_templates/08_scenario_analysis.xlsx
+++ b/src/ii_skills/shared/excel_templates/08_scenario_analysis.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +27,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000A651"/>
+      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -42,8 +53,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+        <bgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF5F5"/>
+        <bgColor rgb="00FFF5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F9FF"/>
+        <bgColor rgb="00F5F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5FFF5"/>
+        <bgColor rgb="00F5FFF5"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,14 +112,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,340 +499,305 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ASSUMPTIONS</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>PROBABILITY WEIGHTING</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Scenario Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SCENARIO ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Bear_Case</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Base_Case</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Bull_Case</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Weighted IRR</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Revenue Growth</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Revenue CAGR (%)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>5.0%</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>8.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Exit EBITDA Margin (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Exit Multiple (x)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>9.5x</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>11.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Probability (%)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>18.0%</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>22.0%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>9.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Exit Multiple</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10.0x</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>12.0x</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Debt Paydown</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hold Period (Years)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>OUTPUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Output_Metric</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Bear_Case</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Base_Case</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Bull_Case</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>CALCULATED OUTPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Exit EBITDA ($M)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>$32</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>$42</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>$55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Exit EV ($M)</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>850</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Equity Value ($M)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>520</v>
-      </c>
-      <c r="C13" t="n">
-        <v>780</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>$256</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>$399</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>$605</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>Exit Equity ($M)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>$165</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>$310</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>$515</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Gross MOIC (x)</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>1.7x</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
           <t>3.2x</t>
         </is>
       </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>5.3x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Gross IRR (%)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>PROBABILITY-WEIGHTED RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Expected Gross MOIC</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>3.1x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Expected Gross IRR</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B4:E4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>